--- a/assets/xl/pg-attendance.xlsx
+++ b/assets/xl/pg-attendance.xlsx
@@ -270,7 +270,7 @@
               <color rgb="FF000000"/>
               <rFont val="Arial"/>
             </rPr>
-            <t xml:space="preserve">3/5/2026 1:02:35 PM</t>
+            <t xml:space="preserve">7/7/2026 9:49:31 AM</t>
           </r>
           <r>
             <rPr>
@@ -294,7 +294,7 @@
               <color rgb="FF000000"/>
               <rFont val="Arial"/>
             </rPr>
-            <t xml:space="preserve">DCI Admin</t>
+            <t xml:space="preserve">Malabar_nodal</t>
           </r>
         </is>
       </c>
@@ -450,12 +450,12 @@
       </c>
       <c s="5" t="inlineStr" r="C6">
         <is>
-          <t xml:space="preserve">Sara Jones</t>
+          <t xml:space="preserve">Punnya A V</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D6">
         <is>
-          <t xml:space="preserve">111100056901</t>
+          <t xml:space="preserve">111100066556</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E6">
@@ -465,33 +465,33 @@
       </c>
       <c s="5" t="inlineStr" r="F6">
         <is>
-          <t xml:space="preserve">Prosthodontics</t>
+          <t xml:space="preserve">Pedodontics</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G6">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H6">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J6">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c s="4" r="K6">
+        <v>0</v>
+      </c>
+      <c s="6" t="inlineStr" r="L6">
+        <is>
+          <t xml:space="preserve">214:09</t>
+        </is>
+      </c>
+      <c s="7" r="M6">
         <v>1</v>
-      </c>
-      <c s="6" t="inlineStr" r="L6">
-        <is>
-          <t xml:space="preserve">230:12</t>
-        </is>
-      </c>
-      <c s="7" r="M6">
-        <v>0.958333333333333</v>
       </c>
     </row>
     <row r="7" ht="17.9" customHeight="0">
@@ -505,12 +505,12 @@
       </c>
       <c s="5" t="inlineStr" r="C7">
         <is>
-          <t xml:space="preserve">Anitta C Raj</t>
+          <t xml:space="preserve">Sara Jones</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D7">
         <is>
-          <t xml:space="preserve">111100056899</t>
+          <t xml:space="preserve">111100056901</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E7">
@@ -525,28 +525,28 @@
       </c>
       <c s="6" t="inlineStr" r="G7">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I7">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c s="4" r="K7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c s="6" t="inlineStr" r="L7">
         <is>
-          <t xml:space="preserve">209:45</t>
+          <t xml:space="preserve">208:27</t>
         </is>
       </c>
       <c s="7" r="M7">
-        <v>0.875</v>
+        <v>0.846153846153846</v>
       </c>
     </row>
     <row r="8" ht="17.85" customHeight="0">
@@ -560,12 +560,12 @@
       </c>
       <c s="5" t="inlineStr" r="C8">
         <is>
-          <t xml:space="preserve">Keerthi K</t>
+          <t xml:space="preserve">Jyotsna K Jose</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D8">
         <is>
-          <t xml:space="preserve">111100056850</t>
+          <t xml:space="preserve">111100044010</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E8">
@@ -575,33 +575,33 @@
       </c>
       <c s="5" t="inlineStr" r="F8">
         <is>
-          <t xml:space="preserve">Orthodontics</t>
+          <t xml:space="preserve">Pedodontics</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G8">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H8">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I8">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J8">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c s="4" r="K8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c s="6" t="inlineStr" r="L8">
         <is>
-          <t xml:space="preserve">196:37</t>
+          <t xml:space="preserve">205:07</t>
         </is>
       </c>
       <c s="7" r="M8">
-        <v>0.916666666666667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="17.9" customHeight="0">
@@ -615,12 +615,12 @@
       </c>
       <c s="5" t="inlineStr" r="C9">
         <is>
-          <t xml:space="preserve">Nabeelah Ibrahim Zainuddeen</t>
+          <t xml:space="preserve">Abhiram B</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D9">
         <is>
-          <t xml:space="preserve">111100066699</t>
+          <t xml:space="preserve">111100066566</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E9">
@@ -630,33 +630,33 @@
       </c>
       <c s="5" t="inlineStr" r="F9">
         <is>
-          <t xml:space="preserve">Orthodontics</t>
+          <t xml:space="preserve">Pedodontics</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G9">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H9">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I9">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J9">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c s="4" r="K9">
+        <v>0</v>
+      </c>
+      <c s="6" t="inlineStr" r="L9">
+        <is>
+          <t xml:space="preserve">204:52</t>
+        </is>
+      </c>
+      <c s="7" r="M9">
         <v>1</v>
-      </c>
-      <c s="6" t="inlineStr" r="L9">
-        <is>
-          <t xml:space="preserve">186:46</t>
-        </is>
-      </c>
-      <c s="7" r="M9">
-        <v>0.958333333333333</v>
       </c>
     </row>
     <row r="10" ht="17.85" customHeight="0">
@@ -670,12 +670,12 @@
       </c>
       <c s="5" t="inlineStr" r="C10">
         <is>
-          <t xml:space="preserve">ANU M PAUL</t>
+          <t xml:space="preserve">Sreelakshmi M S</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D10">
         <is>
-          <t xml:space="preserve">111100056848</t>
+          <t xml:space="preserve">111100066549</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E10">
@@ -685,33 +685,33 @@
       </c>
       <c s="5" t="inlineStr" r="F10">
         <is>
-          <t xml:space="preserve">Orthodontics</t>
+          <t xml:space="preserve">Pedodontics</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G10">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H10">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I10">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J10">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c s="4" r="K10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c s="6" t="inlineStr" r="L10">
         <is>
-          <t xml:space="preserve">182:37</t>
+          <t xml:space="preserve">202:44</t>
         </is>
       </c>
       <c s="7" r="M10">
-        <v>0.875</v>
+        <v>0.961538461538462</v>
       </c>
     </row>
     <row r="11" ht="17.9" customHeight="0">
@@ -725,12 +725,12 @@
       </c>
       <c s="5" t="inlineStr" r="C11">
         <is>
-          <t xml:space="preserve">Kavya Mohan</t>
+          <t xml:space="preserve">M Chandhini Mohan</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D11">
         <is>
-          <t xml:space="preserve">111100066688</t>
+          <t xml:space="preserve">111100066563</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E11">
@@ -740,33 +740,33 @@
       </c>
       <c s="5" t="inlineStr" r="F11">
         <is>
-          <t xml:space="preserve">Orthodontics</t>
+          <t xml:space="preserve">Pedodontics</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G11">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H11">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I11">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J11">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c s="4" r="K11">
         <v>1</v>
       </c>
       <c s="6" t="inlineStr" r="L11">
         <is>
-          <t xml:space="preserve">179:51</t>
+          <t xml:space="preserve">199:45</t>
         </is>
       </c>
       <c s="7" r="M11">
-        <v>0.958333333333333</v>
+        <v>0.961538461538462</v>
       </c>
     </row>
     <row r="12" ht="17.9" customHeight="0">
@@ -780,12 +780,12 @@
       </c>
       <c s="5" t="inlineStr" r="C12">
         <is>
-          <t xml:space="preserve">Anju Prakash</t>
+          <t xml:space="preserve">Parvathy S</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D12">
         <is>
-          <t xml:space="preserve">111100056902</t>
+          <t xml:space="preserve">111100062400</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E12">
@@ -795,33 +795,33 @@
       </c>
       <c s="5" t="inlineStr" r="F12">
         <is>
-          <t xml:space="preserve">Endodontics</t>
+          <t xml:space="preserve">Pedodontics</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G12">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H12">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I12">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J12">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c s="4" r="K12">
         <v>1</v>
       </c>
       <c s="6" t="inlineStr" r="L12">
         <is>
-          <t xml:space="preserve">173:13</t>
+          <t xml:space="preserve">197:35</t>
         </is>
       </c>
       <c s="7" r="M12">
-        <v>0.958333333333333</v>
+        <v>0.961538461538462</v>
       </c>
     </row>
     <row r="13" ht="17.85" customHeight="0">
@@ -835,12 +835,12 @@
       </c>
       <c s="5" t="inlineStr" r="C13">
         <is>
-          <t xml:space="preserve">Jasmina T</t>
+          <t xml:space="preserve">Subili Rehman P</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D13">
         <is>
-          <t xml:space="preserve">111100062398</t>
+          <t xml:space="preserve">111100043314</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E13">
@@ -850,33 +850,33 @@
       </c>
       <c s="5" t="inlineStr" r="F13">
         <is>
-          <t xml:space="preserve">Orthodontics</t>
+          <t xml:space="preserve">Periodontics</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G13">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H13">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I13">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J13">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c s="4" r="K13">
         <v>1</v>
       </c>
       <c s="6" t="inlineStr" r="L13">
         <is>
-          <t xml:space="preserve">172:20</t>
+          <t xml:space="preserve">196:41</t>
         </is>
       </c>
       <c s="7" r="M13">
-        <v>0.958333333333333</v>
+        <v>0.961538461538462</v>
       </c>
     </row>
     <row r="14" ht="17.9" customHeight="0">
@@ -890,12 +890,12 @@
       </c>
       <c s="5" t="inlineStr" r="C14">
         <is>
-          <t xml:space="preserve">M Chandhini Mohan</t>
+          <t xml:space="preserve">Geetha A A</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D14">
         <is>
-          <t xml:space="preserve">111100066563</t>
+          <t xml:space="preserve">111100062399</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E14">
@@ -910,28 +910,28 @@
       </c>
       <c s="6" t="inlineStr" r="G14">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c s="4" r="K14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="6" t="inlineStr" r="L14">
         <is>
-          <t xml:space="preserve">170:30</t>
+          <t xml:space="preserve">189:00</t>
         </is>
       </c>
       <c s="7" r="M14">
-        <v>0.916666666666667</v>
+        <v>0.961538461538462</v>
       </c>
     </row>
     <row r="15" ht="17.85" customHeight="0">
@@ -945,12 +945,12 @@
       </c>
       <c s="5" t="inlineStr" r="C15">
         <is>
-          <t xml:space="preserve">AISWARYA JAYARAM</t>
+          <t xml:space="preserve">Celin Gayose M</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D15">
         <is>
-          <t xml:space="preserve">111100056865</t>
+          <t xml:space="preserve">111100043376</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E15">
@@ -965,28 +965,28 @@
       </c>
       <c s="6" t="inlineStr" r="G15">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H15">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I15">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J15">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c s="4" r="K15">
+        <v>0</v>
+      </c>
+      <c s="6" t="inlineStr" r="L15">
+        <is>
+          <t xml:space="preserve">187:18</t>
+        </is>
+      </c>
+      <c s="7" r="M15">
         <v>1</v>
-      </c>
-      <c s="6" t="inlineStr" r="L15">
-        <is>
-          <t xml:space="preserve">165:19</t>
-        </is>
-      </c>
-      <c s="7" r="M15">
-        <v>0.958333333333333</v>
       </c>
     </row>
     <row r="16" ht="17.9" customHeight="0">
@@ -1000,12 +1000,12 @@
       </c>
       <c s="5" t="inlineStr" r="C16">
         <is>
-          <t xml:space="preserve">Vidya C</t>
+          <t xml:space="preserve">Athulya B Mohan</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D16">
         <is>
-          <t xml:space="preserve">111100056851</t>
+          <t xml:space="preserve">111100043370</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E16">
@@ -1015,33 +1015,33 @@
       </c>
       <c s="5" t="inlineStr" r="F16">
         <is>
-          <t xml:space="preserve">Orthodontics</t>
+          <t xml:space="preserve">Conservative Dentistry</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G16">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H16">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J16">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c s="4" r="K16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c s="6" t="inlineStr" r="L16">
         <is>
-          <t xml:space="preserve">165:19</t>
+          <t xml:space="preserve">185:30</t>
         </is>
       </c>
       <c s="7" r="M16">
-        <v>0.916666666666667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" ht="17.9" customHeight="0">
@@ -1055,12 +1055,12 @@
       </c>
       <c s="5" t="inlineStr" r="C17">
         <is>
-          <t xml:space="preserve">Shifanath K</t>
+          <t xml:space="preserve">Janaki Sathish</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D17">
         <is>
-          <t xml:space="preserve">111100056846</t>
+          <t xml:space="preserve">111100056904</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E17">
@@ -1070,33 +1070,33 @@
       </c>
       <c s="5" t="inlineStr" r="F17">
         <is>
-          <t xml:space="preserve">Orthodontics</t>
+          <t xml:space="preserve">Periodontics</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G17">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H17">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I17">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J17">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c s="4" r="K17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c s="6" t="inlineStr" r="L17">
         <is>
-          <t xml:space="preserve">165:10</t>
+          <t xml:space="preserve">183:39</t>
         </is>
       </c>
       <c s="7" r="M17">
-        <v>0.875</v>
+        <v>0.961538461538462</v>
       </c>
     </row>
     <row r="18" ht="17.85" customHeight="0">
@@ -1110,12 +1110,12 @@
       </c>
       <c s="5" t="inlineStr" r="C18">
         <is>
-          <t xml:space="preserve">Thanvi Shaji</t>
+          <t xml:space="preserve">Anchel Asok</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D18">
         <is>
-          <t xml:space="preserve">111100062404</t>
+          <t xml:space="preserve">111100066528</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E18">
@@ -1125,33 +1125,33 @@
       </c>
       <c s="5" t="inlineStr" r="F18">
         <is>
-          <t xml:space="preserve">Conservative Dentistry</t>
+          <t xml:space="preserve">Prosthodontics</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G18">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H18">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I18">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J18">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c s="4" r="K18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c s="6" t="inlineStr" r="L18">
         <is>
-          <t xml:space="preserve">163:10</t>
+          <t xml:space="preserve">182:12</t>
         </is>
       </c>
       <c s="7" r="M18">
-        <v>0.916666666666667</v>
+        <v>0.884615384615385</v>
       </c>
     </row>
     <row r="19" ht="17.9" customHeight="0">
@@ -1165,12 +1165,12 @@
       </c>
       <c s="5" t="inlineStr" r="C19">
         <is>
-          <t xml:space="preserve">Al Salna</t>
+          <t xml:space="preserve">AISWARYA JAYARAM</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D19">
         <is>
-          <t xml:space="preserve">111100066697</t>
+          <t xml:space="preserve">111100056865</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E19">
@@ -1180,33 +1180,33 @@
       </c>
       <c s="5" t="inlineStr" r="F19">
         <is>
-          <t xml:space="preserve">Orthodontics</t>
+          <t xml:space="preserve">Conservative Dentistry</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G19">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H19">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I19">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J19">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c s="4" r="K19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c s="6" t="inlineStr" r="L19">
         <is>
-          <t xml:space="preserve">161:44</t>
+          <t xml:space="preserve">179:02</t>
         </is>
       </c>
       <c s="7" r="M19">
-        <v>0.875</v>
+        <v>0.961538461538462</v>
       </c>
     </row>
     <row r="20" ht="17.85" customHeight="0">
@@ -1220,12 +1220,12 @@
       </c>
       <c s="5" t="inlineStr" r="C20">
         <is>
-          <t xml:space="preserve">Sreelakshmi M S</t>
+          <t xml:space="preserve">Seenu Shahas</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D20">
         <is>
-          <t xml:space="preserve">111100066549</t>
+          <t xml:space="preserve">111100066553</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E20">
@@ -1240,28 +1240,28 @@
       </c>
       <c s="6" t="inlineStr" r="G20">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H20">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I20">
+        <v>26</v>
+      </c>
+      <c s="4" r="J20">
         <v>24</v>
-      </c>
-      <c s="4" r="J20">
-        <v>22</v>
       </c>
       <c s="4" r="K20">
         <v>2</v>
       </c>
       <c s="6" t="inlineStr" r="L20">
         <is>
-          <t xml:space="preserve">161:28</t>
+          <t xml:space="preserve">175:58</t>
         </is>
       </c>
       <c s="7" r="M20">
-        <v>0.916666666666667</v>
+        <v>0.923076923076923</v>
       </c>
     </row>
     <row r="21" ht="17.9" customHeight="0">
@@ -1275,12 +1275,12 @@
       </c>
       <c s="5" t="inlineStr" r="C21">
         <is>
-          <t xml:space="preserve">Subili Rehman P</t>
+          <t xml:space="preserve">Joe Chacko</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D21">
         <is>
-          <t xml:space="preserve">111100043314</t>
+          <t xml:space="preserve">111100066634</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E21">
@@ -1290,33 +1290,33 @@
       </c>
       <c s="5" t="inlineStr" r="F21">
         <is>
-          <t xml:space="preserve">Periodontics</t>
+          <t xml:space="preserve">Conservative Dentistry</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G21">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H21">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I21">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J21">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c s="4" r="K21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="6" t="inlineStr" r="L21">
         <is>
-          <t xml:space="preserve">161:02</t>
+          <t xml:space="preserve">175:42</t>
         </is>
       </c>
       <c s="7" r="M21">
-        <v>0.916666666666667</v>
+        <v>0.961538461538462</v>
       </c>
     </row>
     <row r="22" ht="17.85" customHeight="0">
@@ -1330,12 +1330,12 @@
       </c>
       <c s="5" t="inlineStr" r="C22">
         <is>
-          <t xml:space="preserve">Athulya B Mohan</t>
+          <t xml:space="preserve">KAVYA SABU</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D22">
         <is>
-          <t xml:space="preserve">111100043370</t>
+          <t xml:space="preserve">111100066631</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E22">
@@ -1350,28 +1350,28 @@
       </c>
       <c s="6" t="inlineStr" r="G22">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H22">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I22">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J22">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c s="4" r="K22">
+        <v>0</v>
+      </c>
+      <c s="6" t="inlineStr" r="L22">
+        <is>
+          <t xml:space="preserve">174:56</t>
+        </is>
+      </c>
+      <c s="7" r="M22">
         <v>1</v>
-      </c>
-      <c s="6" t="inlineStr" r="L22">
-        <is>
-          <t xml:space="preserve">160:08</t>
-        </is>
-      </c>
-      <c s="7" r="M22">
-        <v>0.958333333333333</v>
       </c>
     </row>
     <row r="23" ht="17.9" customHeight="0">
@@ -1405,28 +1405,28 @@
       </c>
       <c s="6" t="inlineStr" r="G23">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H23">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I23">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J23">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c s="4" r="K23">
         <v>1</v>
       </c>
       <c s="6" t="inlineStr" r="L23">
         <is>
-          <t xml:space="preserve">157:20</t>
+          <t xml:space="preserve">173:31</t>
         </is>
       </c>
       <c s="7" r="M23">
-        <v>0.958333333333333</v>
+        <v>0.961538461538462</v>
       </c>
     </row>
     <row r="24" ht="17.9" customHeight="0">
@@ -1440,12 +1440,12 @@
       </c>
       <c s="5" t="inlineStr" r="C24">
         <is>
-          <t xml:space="preserve">Sharanya S</t>
+          <t xml:space="preserve">Anitta C Raj</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D24">
         <is>
-          <t xml:space="preserve">111100066691</t>
+          <t xml:space="preserve">111100056899</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E24">
@@ -1455,33 +1455,33 @@
       </c>
       <c s="5" t="inlineStr" r="F24">
         <is>
-          <t xml:space="preserve">Orthodontics</t>
+          <t xml:space="preserve">Prosthodontics</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G24">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H24">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I24">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J24">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c s="4" r="K24">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c s="6" t="inlineStr" r="L24">
         <is>
-          <t xml:space="preserve">157:14</t>
+          <t xml:space="preserve">171:27</t>
         </is>
       </c>
       <c s="7" r="M24">
-        <v>0.958333333333333</v>
+        <v>0.807692307692308</v>
       </c>
     </row>
     <row r="25" ht="17.85" customHeight="0">
@@ -1495,12 +1495,12 @@
       </c>
       <c s="5" t="inlineStr" r="C25">
         <is>
-          <t xml:space="preserve">Punnya A V</t>
+          <t xml:space="preserve">Thanvi Shaji</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D25">
         <is>
-          <t xml:space="preserve">111100066556</t>
+          <t xml:space="preserve">111100062404</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E25">
@@ -1510,33 +1510,33 @@
       </c>
       <c s="5" t="inlineStr" r="F25">
         <is>
-          <t xml:space="preserve">Pedodontics</t>
+          <t xml:space="preserve">Conservative Dentistry</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G25">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H25">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I25">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J25">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c s="4" r="K25">
         <v>3</v>
       </c>
       <c s="6" t="inlineStr" r="L25">
         <is>
-          <t xml:space="preserve">156:44</t>
+          <t xml:space="preserve">170:33</t>
         </is>
       </c>
       <c s="7" r="M25">
-        <v>0.875</v>
+        <v>0.884615384615385</v>
       </c>
     </row>
     <row r="26" ht="17.9" customHeight="0">
@@ -1550,12 +1550,12 @@
       </c>
       <c s="5" t="inlineStr" r="C26">
         <is>
-          <t xml:space="preserve">Ashli N P</t>
+          <t xml:space="preserve">ANU M PAUL</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D26">
         <is>
-          <t xml:space="preserve">111100066652</t>
+          <t xml:space="preserve">111100056848</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E26">
@@ -1565,33 +1565,33 @@
       </c>
       <c s="5" t="inlineStr" r="F26">
         <is>
-          <t xml:space="preserve">Conservative Dentistry</t>
+          <t xml:space="preserve">Orthodontics</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G26">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H26">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I26">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J26">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c s="4" r="K26">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c s="6" t="inlineStr" r="L26">
         <is>
-          <t xml:space="preserve">156:26</t>
+          <t xml:space="preserve">170:14</t>
         </is>
       </c>
       <c s="7" r="M26">
-        <v>0.916666666666667</v>
+        <v>0.769230769230769</v>
       </c>
     </row>
     <row r="27" ht="17.85" customHeight="0">
@@ -1605,12 +1605,12 @@
       </c>
       <c s="5" t="inlineStr" r="C27">
         <is>
-          <t xml:space="preserve">Joe Chacko</t>
+          <t xml:space="preserve">Ashli N P</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D27">
         <is>
-          <t xml:space="preserve">111100066634</t>
+          <t xml:space="preserve">111100066652</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E27">
@@ -1625,28 +1625,28 @@
       </c>
       <c s="6" t="inlineStr" r="G27">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H27">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I27">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J27">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c s="4" r="K27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="6" t="inlineStr" r="L27">
         <is>
-          <t xml:space="preserve">154:09</t>
+          <t xml:space="preserve">170:06</t>
         </is>
       </c>
       <c s="7" r="M27">
-        <v>0.916666666666667</v>
+        <v>0.961538461538462</v>
       </c>
     </row>
     <row r="28" ht="17.9" customHeight="0">
@@ -1660,12 +1660,12 @@
       </c>
       <c s="5" t="inlineStr" r="C28">
         <is>
-          <t xml:space="preserve">Gautham C Baiju</t>
+          <t xml:space="preserve">Anju Prakash</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D28">
         <is>
-          <t xml:space="preserve">111100062402</t>
+          <t xml:space="preserve">111100056902</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E28">
@@ -1680,28 +1680,28 @@
       </c>
       <c s="6" t="inlineStr" r="G28">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H28">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I28">
+        <v>26</v>
+      </c>
+      <c s="4" r="J28">
         <v>24</v>
-      </c>
-      <c s="4" r="J28">
-        <v>22</v>
       </c>
       <c s="4" r="K28">
         <v>2</v>
       </c>
       <c s="6" t="inlineStr" r="L28">
         <is>
-          <t xml:space="preserve">153:22</t>
+          <t xml:space="preserve">167:51</t>
         </is>
       </c>
       <c s="7" r="M28">
-        <v>0.916666666666667</v>
+        <v>0.923076923076923</v>
       </c>
     </row>
     <row r="29" ht="17.9" customHeight="0">
@@ -1715,12 +1715,12 @@
       </c>
       <c s="5" t="inlineStr" r="C29">
         <is>
-          <t xml:space="preserve">Sajna A</t>
+          <t xml:space="preserve">Gautham C Baiju</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D29">
         <is>
-          <t xml:space="preserve">111100066644</t>
+          <t xml:space="preserve">111100062402</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E29">
@@ -1730,33 +1730,33 @@
       </c>
       <c s="5" t="inlineStr" r="F29">
         <is>
-          <t xml:space="preserve">Conservative Dentistry</t>
+          <t xml:space="preserve">Endodontics</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G29">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H29">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I29">
+        <v>26</v>
+      </c>
+      <c s="4" r="J29">
         <v>24</v>
-      </c>
-      <c s="4" r="J29">
-        <v>22</v>
       </c>
       <c s="4" r="K29">
         <v>2</v>
       </c>
       <c s="6" t="inlineStr" r="L29">
         <is>
-          <t xml:space="preserve">152:32</t>
+          <t xml:space="preserve">167:01</t>
         </is>
       </c>
       <c s="7" r="M29">
-        <v>0.916666666666667</v>
+        <v>0.923076923076923</v>
       </c>
     </row>
     <row r="30" ht="17.85" customHeight="0">
@@ -1770,12 +1770,12 @@
       </c>
       <c s="5" t="inlineStr" r="C30">
         <is>
-          <t xml:space="preserve">Sandeep Murukan</t>
+          <t xml:space="preserve">Shahin Beegum K</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D30">
         <is>
-          <t xml:space="preserve">111100066521</t>
+          <t xml:space="preserve">111100066615</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E30">
@@ -1785,33 +1785,33 @@
       </c>
       <c s="5" t="inlineStr" r="F30">
         <is>
-          <t xml:space="preserve">Prosthodontics</t>
+          <t xml:space="preserve">Oral Pathology</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G30">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H30">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I30">
+        <v>26</v>
+      </c>
+      <c s="4" r="J30">
         <v>24</v>
       </c>
-      <c s="4" r="J30">
-        <v>21</v>
-      </c>
       <c s="4" r="K30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c s="6" t="inlineStr" r="L30">
         <is>
-          <t xml:space="preserve">151:11</t>
+          <t xml:space="preserve">165:20</t>
         </is>
       </c>
       <c s="7" r="M30">
-        <v>0.875</v>
+        <v>0.923076923076923</v>
       </c>
     </row>
     <row r="31" ht="17.9" customHeight="0">
@@ -1825,12 +1825,12 @@
       </c>
       <c s="5" t="inlineStr" r="C31">
         <is>
-          <t xml:space="preserve">Abhiram B</t>
+          <t xml:space="preserve">Al Salna</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D31">
         <is>
-          <t xml:space="preserve">111100066566</t>
+          <t xml:space="preserve">111100066697</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E31">
@@ -1840,33 +1840,33 @@
       </c>
       <c s="5" t="inlineStr" r="F31">
         <is>
-          <t xml:space="preserve">Pedodontics</t>
+          <t xml:space="preserve">Orthodontics</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G31">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H31">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I31">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J31">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c s="4" r="K31">
         <v>4</v>
       </c>
       <c s="6" t="inlineStr" r="L31">
         <is>
-          <t xml:space="preserve">149:53</t>
+          <t xml:space="preserve">165:09</t>
         </is>
       </c>
       <c s="7" r="M31">
-        <v>0.833333333333333</v>
+        <v>0.846153846153846</v>
       </c>
     </row>
     <row r="32" ht="17.85" customHeight="0">
@@ -1880,12 +1880,12 @@
       </c>
       <c s="5" t="inlineStr" r="C32">
         <is>
-          <t xml:space="preserve">Vishak Chand C U</t>
+          <t xml:space="preserve">Snigdha Sadanandan T</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D32">
         <is>
-          <t xml:space="preserve">111100043379</t>
+          <t xml:space="preserve">111100043293</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E32">
@@ -1895,33 +1895,33 @@
       </c>
       <c s="5" t="inlineStr" r="F32">
         <is>
-          <t xml:space="preserve">Conservative Dentistry</t>
+          <t xml:space="preserve">Orthodontics</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G32">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H32">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I32">
+        <v>26</v>
+      </c>
+      <c s="4" r="J32">
         <v>24</v>
       </c>
-      <c s="4" r="J32">
-        <v>23</v>
-      </c>
       <c s="4" r="K32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c s="6" t="inlineStr" r="L32">
         <is>
-          <t xml:space="preserve">149:37</t>
+          <t xml:space="preserve">164:04</t>
         </is>
       </c>
       <c s="7" r="M32">
-        <v>0.958333333333333</v>
+        <v>0.923076923076923</v>
       </c>
     </row>
     <row r="33" ht="17.9" customHeight="0">
@@ -1935,12 +1935,12 @@
       </c>
       <c s="5" t="inlineStr" r="C33">
         <is>
-          <t xml:space="preserve">Sreejith M</t>
+          <t xml:space="preserve">Sandeep Murukan</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D33">
         <is>
-          <t xml:space="preserve">111100066656</t>
+          <t xml:space="preserve">111100066521</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E33">
@@ -1950,33 +1950,33 @@
       </c>
       <c s="5" t="inlineStr" r="F33">
         <is>
-          <t xml:space="preserve">Conservative Dentistry</t>
+          <t xml:space="preserve">Prosthodontics</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G33">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H33">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I33">
+        <v>26</v>
+      </c>
+      <c s="4" r="J33">
         <v>24</v>
       </c>
-      <c s="4" r="J33">
-        <v>21</v>
-      </c>
       <c s="4" r="K33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c s="6" t="inlineStr" r="L33">
         <is>
-          <t xml:space="preserve">148:42</t>
+          <t xml:space="preserve">163:38</t>
         </is>
       </c>
       <c s="7" r="M33">
-        <v>0.875</v>
+        <v>0.923076923076923</v>
       </c>
     </row>
     <row r="34" ht="17.85" customHeight="0">
@@ -2010,28 +2010,28 @@
       </c>
       <c s="6" t="inlineStr" r="G34">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H34">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I34">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J34">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c s="4" r="K34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c s="6" t="inlineStr" r="L34">
         <is>
-          <t xml:space="preserve">147:06</t>
+          <t xml:space="preserve">163:29</t>
         </is>
       </c>
       <c s="7" r="M34">
-        <v>0.875</v>
+        <v>0.961538461538462</v>
       </c>
     </row>
     <row r="35" ht="17.9" customHeight="0">
@@ -2045,12 +2045,12 @@
       </c>
       <c s="5" t="inlineStr" r="C35">
         <is>
-          <t xml:space="preserve">Rohit Jayaraj</t>
+          <t xml:space="preserve">SREEVAS S</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D35">
         <is>
-          <t xml:space="preserve">111100066612</t>
+          <t xml:space="preserve">111100066430</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E35">
@@ -2060,33 +2060,33 @@
       </c>
       <c s="5" t="inlineStr" r="F35">
         <is>
-          <t xml:space="preserve">Oral Pathology</t>
+          <t xml:space="preserve">Periodontics</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G35">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H35">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I35">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J35">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c s="4" r="K35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c s="6" t="inlineStr" r="L35">
         <is>
-          <t xml:space="preserve">145:23</t>
+          <t xml:space="preserve">162:30</t>
         </is>
       </c>
       <c s="7" r="M35">
-        <v>0.916666666666667</v>
+        <v>0.884615384615385</v>
       </c>
     </row>
     <row r="36" ht="17.9" customHeight="0">
@@ -2100,12 +2100,12 @@
       </c>
       <c s="5" t="inlineStr" r="C36">
         <is>
-          <t xml:space="preserve">Sangeethlal.A. V</t>
+          <t xml:space="preserve">VIVEK S</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D36">
         <is>
-          <t xml:space="preserve">111100066437</t>
+          <t xml:space="preserve">111100062401</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E36">
@@ -2115,33 +2115,33 @@
       </c>
       <c s="5" t="inlineStr" r="F36">
         <is>
-          <t xml:space="preserve">Oral Medicine</t>
+          <t xml:space="preserve">Periodontics</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G36">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H36">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I36">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J36">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c s="4" r="K36">
         <v>1</v>
       </c>
       <c s="6" t="inlineStr" r="L36">
         <is>
-          <t xml:space="preserve">144:17</t>
+          <t xml:space="preserve">160:30</t>
         </is>
       </c>
       <c s="7" r="M36">
-        <v>0.958333333333333</v>
+        <v>0.961538461538462</v>
       </c>
     </row>
     <row r="37" ht="17.85" customHeight="0">
@@ -2155,12 +2155,12 @@
       </c>
       <c s="5" t="inlineStr" r="C37">
         <is>
-          <t xml:space="preserve">Janaki Sathish</t>
+          <t xml:space="preserve">Joel Joju C</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D37">
         <is>
-          <t xml:space="preserve">111100056904</t>
+          <t xml:space="preserve">111100066433</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E37">
@@ -2175,28 +2175,28 @@
       </c>
       <c s="6" t="inlineStr" r="G37">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H37">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I37">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J37">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c s="4" r="K37">
         <v>3</v>
       </c>
       <c s="6" t="inlineStr" r="L37">
         <is>
-          <t xml:space="preserve">143:16</t>
+          <t xml:space="preserve">160:23</t>
         </is>
       </c>
       <c s="7" r="M37">
-        <v>0.875</v>
+        <v>0.884615384615385</v>
       </c>
     </row>
     <row r="38" ht="17.9" customHeight="0">
@@ -2210,12 +2210,12 @@
       </c>
       <c s="5" t="inlineStr" r="C38">
         <is>
-          <t xml:space="preserve">Shahin Beegum K</t>
+          <t xml:space="preserve">Kavya Mohan</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D38">
         <is>
-          <t xml:space="preserve">111100066615</t>
+          <t xml:space="preserve">111100066688</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E38">
@@ -2225,33 +2225,33 @@
       </c>
       <c s="5" t="inlineStr" r="F38">
         <is>
-          <t xml:space="preserve">Oral Pathology</t>
+          <t xml:space="preserve">Orthodontics</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G38">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H38">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I38">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J38">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c s="4" r="K38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c s="6" t="inlineStr" r="L38">
         <is>
-          <t xml:space="preserve">142:11</t>
+          <t xml:space="preserve">159:55</t>
         </is>
       </c>
       <c s="7" r="M38">
-        <v>0.875</v>
+        <v>0.846153846153846</v>
       </c>
     </row>
     <row r="39" ht="17.85" customHeight="0">
@@ -2265,12 +2265,12 @@
       </c>
       <c s="5" t="inlineStr" r="C39">
         <is>
-          <t xml:space="preserve">Joel Joju C</t>
+          <t xml:space="preserve">Yadhu Govind M</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D39">
         <is>
-          <t xml:space="preserve">111100066433</t>
+          <t xml:space="preserve">111100056844</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E39">
@@ -2280,33 +2280,33 @@
       </c>
       <c s="5" t="inlineStr" r="F39">
         <is>
-          <t xml:space="preserve">Periodontics</t>
+          <t xml:space="preserve">Pedodontics</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G39">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H39">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I39">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J39">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c s="4" r="K39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c s="6" t="inlineStr" r="L39">
         <is>
-          <t xml:space="preserve">141:58</t>
+          <t xml:space="preserve">157:17</t>
         </is>
       </c>
       <c s="7" r="M39">
-        <v>0.875</v>
+        <v>0.961538461538462</v>
       </c>
     </row>
     <row r="40" ht="17.9" customHeight="0">
@@ -2320,12 +2320,12 @@
       </c>
       <c s="5" t="inlineStr" r="C40">
         <is>
-          <t xml:space="preserve">SREEVAS S</t>
+          <t xml:space="preserve">Sharanya S</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D40">
         <is>
-          <t xml:space="preserve">111100066430</t>
+          <t xml:space="preserve">111100066691</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E40">
@@ -2335,33 +2335,33 @@
       </c>
       <c s="5" t="inlineStr" r="F40">
         <is>
-          <t xml:space="preserve">Periodontics</t>
+          <t xml:space="preserve">Orthodontics</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G40">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H40">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I40">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J40">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c s="4" r="K40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c s="6" t="inlineStr" r="L40">
         <is>
-          <t xml:space="preserve">139:19</t>
+          <t xml:space="preserve">157:04</t>
         </is>
       </c>
       <c s="7" r="M40">
-        <v>0.833333333333333</v>
+        <v>0.807692307692308</v>
       </c>
     </row>
     <row r="41" ht="17.85" customHeight="0">
@@ -2375,12 +2375,12 @@
       </c>
       <c s="5" t="inlineStr" r="C41">
         <is>
-          <t xml:space="preserve">Jyotsna K Jose</t>
+          <t xml:space="preserve">Rahmath Snuba Shareef</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D41">
         <is>
-          <t xml:space="preserve">111100044010</t>
+          <t xml:space="preserve">111100056884</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E41">
@@ -2395,28 +2395,28 @@
       </c>
       <c s="6" t="inlineStr" r="G41">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H41">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I41">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J41">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c s="4" r="K41">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c s="6" t="inlineStr" r="L41">
         <is>
-          <t xml:space="preserve">136:01</t>
+          <t xml:space="preserve">156:38</t>
         </is>
       </c>
       <c s="7" r="M41">
-        <v>0.833333333333333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" ht="17.9" customHeight="0">
@@ -2430,12 +2430,12 @@
       </c>
       <c s="5" t="inlineStr" r="C42">
         <is>
-          <t xml:space="preserve">Geetha A A</t>
+          <t xml:space="preserve">Sajna P S</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D42">
         <is>
-          <t xml:space="preserve">111100062399</t>
+          <t xml:space="preserve">111100066534</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E42">
@@ -2445,33 +2445,33 @@
       </c>
       <c s="5" t="inlineStr" r="F42">
         <is>
-          <t xml:space="preserve">Pedodontics</t>
+          <t xml:space="preserve">Oral Medicine</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G42">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H42">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I42">
+        <v>26</v>
+      </c>
+      <c s="4" r="J42">
         <v>24</v>
       </c>
-      <c s="4" r="J42">
-        <v>16</v>
-      </c>
       <c s="4" r="K42">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c s="6" t="inlineStr" r="L42">
         <is>
-          <t xml:space="preserve">133:09</t>
+          <t xml:space="preserve">156:08</t>
         </is>
       </c>
       <c s="7" r="M42">
-        <v>0.666666666666667</v>
+        <v>0.923076923076923</v>
       </c>
     </row>
     <row r="43" ht="17.9" customHeight="0">
@@ -2485,12 +2485,12 @@
       </c>
       <c s="5" t="inlineStr" r="C43">
         <is>
-          <t xml:space="preserve">Sajna P S</t>
+          <t xml:space="preserve">Shifanath K</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D43">
         <is>
-          <t xml:space="preserve">111100066534</t>
+          <t xml:space="preserve">111100056846</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E43">
@@ -2500,33 +2500,33 @@
       </c>
       <c s="5" t="inlineStr" r="F43">
         <is>
-          <t xml:space="preserve">Oral Medicine</t>
+          <t xml:space="preserve">Orthodontics</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G43">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H43">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I43">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J43">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c s="4" r="K43">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c s="6" t="inlineStr" r="L43">
         <is>
-          <t xml:space="preserve">132:56</t>
+          <t xml:space="preserve">155:16</t>
         </is>
       </c>
       <c s="7" r="M43">
-        <v>0.875</v>
+        <v>0.692307692307692</v>
       </c>
     </row>
     <row r="44" ht="17.85" customHeight="0">
@@ -2560,28 +2560,28 @@
       </c>
       <c s="6" t="inlineStr" r="G44">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H44">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I44">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J44">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c s="4" r="K44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c s="6" t="inlineStr" r="L44">
         <is>
-          <t xml:space="preserve">132:39</t>
+          <t xml:space="preserve">154:23</t>
         </is>
       </c>
       <c s="7" r="M44">
-        <v>0.833333333333333</v>
+        <v>0.807692307692308</v>
       </c>
     </row>
     <row r="45" ht="17.9" customHeight="0">
@@ -2595,12 +2595,12 @@
       </c>
       <c s="5" t="inlineStr" r="C45">
         <is>
-          <t xml:space="preserve">Athira Babu</t>
+          <t xml:space="preserve">Keerthi K</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D45">
         <is>
-          <t xml:space="preserve">111100056841</t>
+          <t xml:space="preserve">111100056850</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E45">
@@ -2610,33 +2610,33 @@
       </c>
       <c s="5" t="inlineStr" r="F45">
         <is>
-          <t xml:space="preserve">Pedodontics</t>
+          <t xml:space="preserve">Orthodontics</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G45">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H45">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I45">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J45">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c s="4" r="K45">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c s="6" t="inlineStr" r="L45">
         <is>
-          <t xml:space="preserve">132:00</t>
+          <t xml:space="preserve">150:36</t>
         </is>
       </c>
       <c s="7" r="M45">
-        <v>0.833333333333333</v>
+        <v>0.730769230769231</v>
       </c>
     </row>
     <row r="46" ht="17.85" customHeight="0">
@@ -2650,12 +2650,12 @@
       </c>
       <c s="5" t="inlineStr" r="C46">
         <is>
-          <t xml:space="preserve">VIVEK S</t>
+          <t xml:space="preserve">Sreejith M</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D46">
         <is>
-          <t xml:space="preserve">111100062401</t>
+          <t xml:space="preserve">111100066656</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E46">
@@ -2665,33 +2665,33 @@
       </c>
       <c s="5" t="inlineStr" r="F46">
         <is>
-          <t xml:space="preserve">Periodontics</t>
+          <t xml:space="preserve">Conservative Dentistry</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G46">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H46">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I46">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J46">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c s="4" r="K46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c s="6" t="inlineStr" r="L46">
         <is>
-          <t xml:space="preserve">126:24</t>
+          <t xml:space="preserve">150:06</t>
         </is>
       </c>
       <c s="7" r="M46">
-        <v>0.833333333333333</v>
+        <v>0.884615384615385</v>
       </c>
     </row>
     <row r="47" ht="17.9" customHeight="0">
@@ -2705,12 +2705,12 @@
       </c>
       <c s="5" t="inlineStr" r="C47">
         <is>
-          <t xml:space="preserve">Anchel Asok</t>
+          <t xml:space="preserve">Nabeelah Ibrahim Zainuddeen</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D47">
         <is>
-          <t xml:space="preserve">111100066528</t>
+          <t xml:space="preserve">111100066699</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E47">
@@ -2720,33 +2720,33 @@
       </c>
       <c s="5" t="inlineStr" r="F47">
         <is>
-          <t xml:space="preserve">Prosthodontics</t>
+          <t xml:space="preserve">Orthodontics</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G47">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H47">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I47">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J47">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c s="4" r="K47">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c s="6" t="inlineStr" r="L47">
         <is>
-          <t xml:space="preserve">117:00</t>
+          <t xml:space="preserve">149:43</t>
         </is>
       </c>
       <c s="7" r="M47">
-        <v>0.958333333333333</v>
+        <v>0.769230769230769</v>
       </c>
     </row>
     <row r="48" ht="17.9" customHeight="0">
@@ -2760,12 +2760,12 @@
       </c>
       <c s="5" t="inlineStr" r="C48">
         <is>
-          <t xml:space="preserve">Snigdha Sadanandan T</t>
+          <t xml:space="preserve">Sangeethlal.A. V</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D48">
         <is>
-          <t xml:space="preserve">111100043293</t>
+          <t xml:space="preserve">111100066437</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E48">
@@ -2775,33 +2775,33 @@
       </c>
       <c s="5" t="inlineStr" r="F48">
         <is>
-          <t xml:space="preserve">Orthodontics</t>
+          <t xml:space="preserve">Oral Medicine</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G48">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H48">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I48">
+        <v>26</v>
+      </c>
+      <c s="4" r="J48">
         <v>24</v>
       </c>
-      <c s="4" r="J48">
-        <v>21</v>
-      </c>
       <c s="4" r="K48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c s="6" t="inlineStr" r="L48">
         <is>
-          <t xml:space="preserve">113:30</t>
+          <t xml:space="preserve">146:09</t>
         </is>
       </c>
       <c s="7" r="M48">
-        <v>0.875</v>
+        <v>0.923076923076923</v>
       </c>
     </row>
     <row r="49" ht="17.85" customHeight="0">
@@ -2815,12 +2815,12 @@
       </c>
       <c s="5" t="inlineStr" r="C49">
         <is>
-          <t xml:space="preserve">Leena Mohammed C</t>
+          <t xml:space="preserve">Rohit Jayaraj</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D49">
         <is>
-          <t xml:space="preserve">111100056843</t>
+          <t xml:space="preserve">111100066612</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E49">
@@ -2830,33 +2830,33 @@
       </c>
       <c s="5" t="inlineStr" r="F49">
         <is>
-          <t xml:space="preserve">Pedodontics</t>
+          <t xml:space="preserve">Oral Pathology</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G49">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H49">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I49">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J49">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c s="4" r="K49">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c s="6" t="inlineStr" r="L49">
         <is>
-          <t xml:space="preserve">111:49</t>
+          <t xml:space="preserve">143:26</t>
         </is>
       </c>
       <c s="7" r="M49">
-        <v>0.75</v>
+        <v>0.884615384615385</v>
       </c>
     </row>
     <row r="50" ht="17.9" customHeight="0">
@@ -2870,12 +2870,12 @@
       </c>
       <c s="5" t="inlineStr" r="C50">
         <is>
-          <t xml:space="preserve">Neethu I M</t>
+          <t xml:space="preserve">Vidya C</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D50">
         <is>
-          <t xml:space="preserve">111100043319</t>
+          <t xml:space="preserve">111100056851</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E50">
@@ -2885,33 +2885,33 @@
       </c>
       <c s="5" t="inlineStr" r="F50">
         <is>
-          <t xml:space="preserve">Prosthodontics</t>
+          <t xml:space="preserve">Orthodontics</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G50">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H50">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I50">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J50">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c s="4" r="K50">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c s="6" t="inlineStr" r="L50">
         <is>
-          <t xml:space="preserve">111:17</t>
+          <t xml:space="preserve">137:58</t>
         </is>
       </c>
       <c s="7" r="M50">
-        <v>0.916666666666667</v>
+        <v>0.807692307692308</v>
       </c>
     </row>
     <row r="51" ht="17.85" customHeight="0">
@@ -2925,12 +2925,12 @@
       </c>
       <c s="5" t="inlineStr" r="C51">
         <is>
-          <t xml:space="preserve">Seenu Shahas</t>
+          <t xml:space="preserve">Nismath</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D51">
         <is>
-          <t xml:space="preserve">111100066553</t>
+          <t xml:space="preserve">111100043863</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E51">
@@ -2940,33 +2940,33 @@
       </c>
       <c s="5" t="inlineStr" r="F51">
         <is>
-          <t xml:space="preserve">Pedodontics</t>
+          <t xml:space="preserve">Orthodontics</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G51">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H51">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I51">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J51">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c s="4" r="K51">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c s="6" t="inlineStr" r="L51">
         <is>
-          <t xml:space="preserve">95:17</t>
+          <t xml:space="preserve">137:03</t>
         </is>
       </c>
       <c s="7" r="M51">
-        <v>0.625</v>
+        <v>0.846153846153846</v>
       </c>
     </row>
     <row r="52" ht="17.9" customHeight="0">
@@ -2980,12 +2980,12 @@
       </c>
       <c s="5" t="inlineStr" r="C52">
         <is>
-          <t xml:space="preserve">KAVYA SABU</t>
+          <t xml:space="preserve">Sajna A</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D52">
         <is>
-          <t xml:space="preserve">111100066631</t>
+          <t xml:space="preserve">111100066644</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E52">
@@ -3000,28 +3000,28 @@
       </c>
       <c s="6" t="inlineStr" r="G52">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H52">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I52">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J52">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c s="4" r="K52">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c s="6" t="inlineStr" r="L52">
         <is>
-          <t xml:space="preserve">93:36</t>
+          <t xml:space="preserve">136:02</t>
         </is>
       </c>
       <c s="7" r="M52">
-        <v>0.708333333333333</v>
+        <v>0.807692307692308</v>
       </c>
     </row>
     <row r="53" ht="17.85" customHeight="0">
@@ -3035,12 +3035,12 @@
       </c>
       <c s="5" t="inlineStr" r="C53">
         <is>
-          <t xml:space="preserve">Yadhu Govind M</t>
+          <t xml:space="preserve">Leena Mohammed C</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D53">
         <is>
-          <t xml:space="preserve">111100056844</t>
+          <t xml:space="preserve">111100056843</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E53">
@@ -3055,28 +3055,28 @@
       </c>
       <c s="6" t="inlineStr" r="G53">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H53">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I53">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J53">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c s="4" r="K53">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c s="6" t="inlineStr" r="L53">
         <is>
-          <t xml:space="preserve">91:37</t>
+          <t xml:space="preserve">134:02</t>
         </is>
       </c>
       <c s="7" r="M53">
-        <v>0.916666666666667</v>
+        <v>0.769230769230769</v>
       </c>
     </row>
     <row r="54" ht="17.9" customHeight="0">
@@ -3090,12 +3090,12 @@
       </c>
       <c s="5" t="inlineStr" r="C54">
         <is>
-          <t xml:space="preserve">Parvathy S</t>
+          <t xml:space="preserve">Jasmina T</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D54">
         <is>
-          <t xml:space="preserve">111100062400</t>
+          <t xml:space="preserve">111100062398</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E54">
@@ -3105,33 +3105,33 @@
       </c>
       <c s="5" t="inlineStr" r="F54">
         <is>
-          <t xml:space="preserve">Pedodontics</t>
+          <t xml:space="preserve">Orthodontics</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G54">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H54">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I54">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J54">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c s="4" r="K54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c s="6" t="inlineStr" r="L54">
         <is>
-          <t xml:space="preserve">90:32</t>
+          <t xml:space="preserve">129:19</t>
         </is>
       </c>
       <c s="7" r="M54">
-        <v>0.791666666666667</v>
+        <v>0.769230769230769</v>
       </c>
     </row>
     <row r="55" ht="17.9" customHeight="0">
@@ -3145,12 +3145,12 @@
       </c>
       <c s="5" t="inlineStr" r="C55">
         <is>
-          <t xml:space="preserve">Nismath</t>
+          <t xml:space="preserve">Vishak Chand C U</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D55">
         <is>
-          <t xml:space="preserve">111100043863</t>
+          <t xml:space="preserve">111100043379</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E55">
@@ -3160,33 +3160,33 @@
       </c>
       <c s="5" t="inlineStr" r="F55">
         <is>
-          <t xml:space="preserve">Orthodontics</t>
+          <t xml:space="preserve">Conservative Dentistry</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G55">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H55">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I55">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J55">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c s="4" r="K55">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c s="6" t="inlineStr" r="L55">
         <is>
-          <t xml:space="preserve">80:46</t>
+          <t xml:space="preserve">127:29</t>
         </is>
       </c>
       <c s="7" r="M55">
-        <v>0.833333333333333</v>
+        <v>0.961538461538462</v>
       </c>
     </row>
     <row r="56" ht="17.85" customHeight="0">
@@ -3200,12 +3200,12 @@
       </c>
       <c s="5" t="inlineStr" r="C56">
         <is>
-          <t xml:space="preserve">Subhna P P</t>
+          <t xml:space="preserve">Athira Babu</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D56">
         <is>
-          <t xml:space="preserve">111100043864</t>
+          <t xml:space="preserve">111100056841</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E56">
@@ -3215,33 +3215,33 @@
       </c>
       <c s="5" t="inlineStr" r="F56">
         <is>
-          <t xml:space="preserve">Periodontics</t>
+          <t xml:space="preserve">Pedodontics</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G56">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H56">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I56">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J56">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c s="4" r="K56">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c s="6" t="inlineStr" r="L56">
         <is>
-          <t xml:space="preserve">67:30</t>
+          <t xml:space="preserve">112:47</t>
         </is>
       </c>
       <c s="7" r="M56">
-        <v>0.916666666666667</v>
+        <v>0.653846153846154</v>
       </c>
     </row>
     <row r="57" ht="17.9" customHeight="0">
@@ -3255,12 +3255,12 @@
       </c>
       <c s="5" t="inlineStr" r="C57">
         <is>
-          <t xml:space="preserve">Akshai C B</t>
+          <t xml:space="preserve">Subhna P P</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D57">
         <is>
-          <t xml:space="preserve">111100043870</t>
+          <t xml:space="preserve">111100043864</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E57">
@@ -3270,33 +3270,33 @@
       </c>
       <c s="5" t="inlineStr" r="F57">
         <is>
-          <t xml:space="preserve">Prosthodontics</t>
+          <t xml:space="preserve">Periodontics</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G57">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H57">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I57">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J57">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c s="4" r="K57">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c s="6" t="inlineStr" r="L57">
         <is>
-          <t xml:space="preserve">59:52</t>
+          <t xml:space="preserve">98:00</t>
         </is>
       </c>
       <c s="7" r="M57">
-        <v>0.708333333333333</v>
+        <v>0.807692307692308</v>
       </c>
     </row>
     <row r="58" ht="17.85" customHeight="0">
@@ -3310,12 +3310,12 @@
       </c>
       <c s="5" t="inlineStr" r="C58">
         <is>
-          <t xml:space="preserve">Celin Gayose M</t>
+          <t xml:space="preserve">Akshai C B</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D58">
         <is>
-          <t xml:space="preserve">111100043376</t>
+          <t xml:space="preserve">111100043870</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E58">
@@ -3325,33 +3325,33 @@
       </c>
       <c s="5" t="inlineStr" r="F58">
         <is>
-          <t xml:space="preserve">Conservative Dentistry</t>
+          <t xml:space="preserve">Prosthodontics</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G58">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H58">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I58">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J58">
+        <v>18</v>
+      </c>
+      <c s="4" r="K58">
         <v>8</v>
       </c>
-      <c s="4" r="K58">
-        <v>16</v>
-      </c>
       <c s="6" t="inlineStr" r="L58">
         <is>
-          <t xml:space="preserve">50:20</t>
+          <t xml:space="preserve">86:06</t>
         </is>
       </c>
       <c s="7" r="M58">
-        <v>0.333333333333333</v>
+        <v>0.692307692307692</v>
       </c>
     </row>
     <row r="59" ht="17.9" customHeight="0">
@@ -3365,12 +3365,12 @@
       </c>
       <c s="5" t="inlineStr" r="C59">
         <is>
-          <t xml:space="preserve">Rahmath Snuba Shareef</t>
+          <t xml:space="preserve">Neethu I M</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="D59">
         <is>
-          <t xml:space="preserve">111100056884</t>
+          <t xml:space="preserve">111100043319</t>
         </is>
       </c>
       <c s="5" t="inlineStr" r="E59">
@@ -3380,33 +3380,33 @@
       </c>
       <c s="5" t="inlineStr" r="F59">
         <is>
-          <t xml:space="preserve">Pedodontics</t>
+          <t xml:space="preserve">Prosthodontics</t>
         </is>
       </c>
       <c s="6" t="inlineStr" r="G59">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H59">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I59">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J59">
+        <v>21</v>
+      </c>
+      <c s="4" r="K59">
         <v>5</v>
       </c>
-      <c s="4" r="K59">
-        <v>19</v>
-      </c>
       <c s="6" t="inlineStr" r="L59">
         <is>
-          <t xml:space="preserve">35:08</t>
+          <t xml:space="preserve">50:38</t>
         </is>
       </c>
       <c s="7" r="M59">
-        <v>0.208333333333333</v>
+        <v>0.807692307692308</v>
       </c>
     </row>
     <row r="60" ht="17.85" customHeight="0">
@@ -3440,20 +3440,20 @@
       </c>
       <c s="6" t="inlineStr" r="G60">
         <is>
-          <t xml:space="preserve">02/2026</t>
+          <t xml:space="preserve">06/2026</t>
         </is>
       </c>
       <c s="4" r="H60">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c s="4" r="I60">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="4" r="J60">
         <v>0</v>
       </c>
       <c s="4" r="K60">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c s="6" t="inlineStr" r="L60">
         <is>
